--- a/SS_low_crested_rubblemound_input.xlsx
+++ b/SS_low_crested_rubblemound_input.xlsx
@@ -1,25 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\0_StormSim_Task\StormSim-Library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F531F7AF-F194-45A1-9900-536046E71933}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4B9EE98-3C83-4A19-8C11-B5115B12051A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{DF680589-5370-4D92-A3AE-D910B140CCC4}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Rubblemound" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -38,397 +35,397 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="131">
   <si>
+    <t>StormSim Project General Inputs</t>
+  </si>
+  <si>
+    <t>StormSim: Monte Carlo Simulation (MCS) Module Inputs</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Model Variable Symbol</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Units</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Field Names</t>
+  </si>
+  <si>
+    <t>project_name</t>
+  </si>
+  <si>
+    <t>Project name</t>
+  </si>
+  <si>
     <t>NA</t>
   </si>
   <si>
-    <t>compute_damaging_depth_slope</t>
+    <t>Chicago Shoreline GRR</t>
+  </si>
+  <si>
+    <t>mcs_nLC</t>
+  </si>
+  <si>
+    <t>Number Of Life Cycles</t>
+  </si>
+  <si>
+    <t>struc_id</t>
+  </si>
+  <si>
+    <t>Structure/Trasnsect ID</t>
+  </si>
+  <si>
+    <t>R7175_T3</t>
+  </si>
+  <si>
+    <t>mcs_nYears</t>
+  </si>
+  <si>
+    <t>Number Of Years To Be Simulated In A Life Cycle</t>
+  </si>
+  <si>
+    <t>[years]</t>
+  </si>
+  <si>
+    <t>case_name</t>
+  </si>
+  <si>
+    <t>Case Name</t>
+  </si>
+  <si>
+    <t>Seawall_existing</t>
+  </si>
+  <si>
+    <t>outfolder</t>
+  </si>
+  <si>
+    <t>StormSim Project output folder.</t>
+  </si>
+  <si>
+    <t>SS_Outputs_7175_T3</t>
+  </si>
+  <si>
+    <t>StormSim: Probabilistic Run-up, Overtopping &amp; Stone Sizing (PROS)</t>
+  </si>
+  <si>
+    <t>project_datum</t>
+  </si>
+  <si>
+    <t>Project output datum. (Still not implemented. Used for plot title currently)</t>
+  </si>
+  <si>
+    <t>IGLD85</t>
+  </si>
+  <si>
+    <t>project_CLs</t>
+  </si>
+  <si>
+    <t>Percentiles to compute CLs (max 4, 50 is already being calculated)</t>
+  </si>
+  <si>
+    <t>[84 90]</t>
+  </si>
+  <si>
+    <t>pros_compute_forcing_HC</t>
+  </si>
+  <si>
+    <t>Compute Hazard for Waves and WL (1 - On, 2 - Off)</t>
+  </si>
+  <si>
+    <t>workflow</t>
+  </si>
+  <si>
+    <t>StormSim workflow to call for project. (1 - StormSim:PROS , 3- StormSim:LCS, 4- StormSim: PROS Frequency Base (FB))</t>
+  </si>
+  <si>
+    <t>pros_use_aep</t>
+  </si>
+  <si>
+    <t>Use AEP or AEF for hazard curves (1 - AEP, 0-AEF)</t>
+  </si>
+  <si>
+    <t>struc_type</t>
+  </si>
+  <si>
+    <t>Structure type  (Levee - 1, Floodwalls - 2, Rubblemound - 3, Low-Crested Breakwater - 4)</t>
+  </si>
+  <si>
+    <t>pros_plot_hc</t>
+  </si>
+  <si>
+    <t>Plot individual responses hazard curves (0 - Off, 1 - On)</t>
+  </si>
+  <si>
+    <t>storm_sampling</t>
+  </si>
+  <si>
+    <t>Storm sampling scheme to use for project. (XC,TC or CC)</t>
+  </si>
+  <si>
+    <t>XC</t>
+  </si>
+  <si>
+    <t>pros_plot_forcing_hc_w_pot</t>
+  </si>
+  <si>
+    <t>Plot forcing hazard curves with corresponding POT sample (0 - Off, 1 - On)</t>
+  </si>
+  <si>
+    <t>swl_slr</t>
+  </si>
+  <si>
+    <t>Sea level rise applied as vertical offset to SWL.</t>
+  </si>
+  <si>
+    <t>[m]</t>
+  </si>
+  <si>
+    <t>pros_plot_prioty_comp</t>
+  </si>
+  <si>
+    <t>Plot RB1 priority datasets responses comparison (0 - Off, 1 - On)</t>
+  </si>
+  <si>
+    <t>apply_random_tides</t>
+  </si>
+  <si>
+    <t>Apply random tide to storm SWL (0 - Off / 1 - On)</t>
+  </si>
+  <si>
+    <t>pros_plot_hc_xsec</t>
+  </si>
+  <si>
+    <t>Plot hazard curve cross section plots (0 - Off, 1 - On)</t>
+  </si>
+  <si>
+    <t>apply_depth_limitation</t>
+  </si>
+  <si>
+    <t>Apply Depth Limitation To Waves  (0 - Off / 1 - On)</t>
+  </si>
+  <si>
+    <t>use_peaks</t>
+  </si>
+  <si>
+    <t>Include forcing peaks files as part of the analysis.  (0 - Off / 1 - On)</t>
+  </si>
+  <si>
+    <t>use_timeseries</t>
+  </si>
+  <si>
+    <t>Include forcing timeseries files as part of the analysis.  (0 - Off / 1 - On)</t>
+  </si>
+  <si>
+    <t>create_wlp</t>
+  </si>
+  <si>
+    <t>Create Water Level Priority Peaks Dataset (WLP)  (0 - Off / 1 - On). (Requires peaks and timeseries files)</t>
+  </si>
+  <si>
+    <t>create_whp</t>
+  </si>
+  <si>
+    <t>Create Wave Height Priority Peaks Dataset (WLP)  (0 - Off / 1 - On). (Requires peaks and timeseries files)</t>
+  </si>
+  <si>
+    <t>create_plots</t>
+  </si>
+  <si>
+    <t>Generate output visualizations (0 - Off, 1 - On)</t>
+  </si>
+  <si>
+    <t>load_project_forcing</t>
+  </si>
+  <si>
+    <t>Load project_forcing StormSim File From Other case_name Under The Same project_name (0- Sample New Storms/1-Load Previous Storm Suite)</t>
+  </si>
+  <si>
+    <t>ref_case_name</t>
+  </si>
+  <si>
+    <t>Define Reference case_name To Load project_forcing From</t>
+  </si>
+  <si>
+    <t>none</t>
+  </si>
+  <si>
+    <t>StormSim Project Forcing Data</t>
+  </si>
+  <si>
+    <t>storm_duration</t>
+  </si>
+  <si>
+    <t>Storm duration.</t>
+  </si>
+  <si>
+    <t>hrs</t>
+  </si>
+  <si>
+    <t>chs_sp_depth</t>
+  </si>
+  <si>
+    <t>CHS savepoint depth (Will be used if not found in h5)</t>
+  </si>
+  <si>
+    <t>m</t>
+  </si>
+  <si>
+    <t>chs_dependencies</t>
+  </si>
+  <si>
+    <t>CHS regional dependencies folder</t>
+  </si>
+  <si>
+    <t>..\CHS_Dependencies</t>
+  </si>
+  <si>
+    <t>chs_zip</t>
+  </si>
+  <si>
+    <t>CHS Zip Folder or Custom Modeling .mat File (Relative Path)</t>
+  </si>
+  <si>
+    <t>Chicago_files\CHS-GLMH_XH_SimBslc0_Post0_SP37697_Timeseries.zip</t>
+  </si>
+  <si>
+    <t>tide_file</t>
+  </si>
+  <si>
+    <t>Tidal file used to randomly sample tidal values for storm SWL. (Relative Path)</t>
+  </si>
+  <si>
+    <t>Structure Geometry</t>
+  </si>
+  <si>
+    <t>crest_elevation</t>
+  </si>
+  <si>
+    <t>Crest Elevation/Top of Wall Elevation</t>
+  </si>
+  <si>
+    <t>crest_width</t>
+  </si>
+  <si>
+    <t>Crest Width/Wall Width</t>
+  </si>
+  <si>
+    <t>toe_elevation</t>
+  </si>
+  <si>
+    <t>Mound Toe Elevation (Negative Below Datum Zero)</t>
+  </si>
+  <si>
+    <t>seaside_slope</t>
+  </si>
+  <si>
+    <t>Mound/Berm Seaward Slope (cota)</t>
+  </si>
+  <si>
+    <t>leeside_slope</t>
+  </si>
+  <si>
+    <t>Mound Landward Slope (cota)</t>
+  </si>
+  <si>
+    <t>Structure Properties</t>
+  </si>
+  <si>
+    <t>armor_delta</t>
+  </si>
+  <si>
+    <t>Armor Immersed Relative Density Delta</t>
+  </si>
+  <si>
+    <t>seaside_mass</t>
+  </si>
+  <si>
+    <t>Seaside Stone Mass</t>
+  </si>
+  <si>
+    <t>[kg]</t>
+  </si>
+  <si>
+    <t>water_density</t>
+  </si>
+  <si>
+    <t>Water Density</t>
+  </si>
+  <si>
+    <t>[kg/m^3]</t>
+  </si>
+  <si>
+    <t>cem_P</t>
+  </si>
+  <si>
+    <t>Mean Value Of Structure Notational Permeability Coefficient (P)</t>
+  </si>
+  <si>
+    <t>[Figure VI-5-11 CEM]</t>
+  </si>
+  <si>
+    <t>roughness_ifactor</t>
+  </si>
+  <si>
+    <t>Roughness Coefficient, 2 for grass; 1 for concrete, asphalt, or closed blocks; 0.9 for basalt or placed revetment blocks; 0.8 for stepped structure; Table 6.2 from EurOtop (2018) (rubble mound )</t>
+  </si>
+  <si>
+    <t>Structure Responses</t>
+  </si>
+  <si>
+    <t>compute_dn50_lcbw</t>
+  </si>
+  <si>
+    <t>Compute Seaward Median Stone Size Response (Low Crested Breakwater)</t>
+  </si>
+  <si>
+    <t>compute_r2p</t>
+  </si>
+  <si>
+    <t>Compute Run-up Response (Eurotop)</t>
+  </si>
+  <si>
+    <t>compute_wave_transmission</t>
+  </si>
+  <si>
+    <t>Compute wave transmission (eurotop)</t>
+  </si>
+  <si>
+    <t>compute_q</t>
+  </si>
+  <si>
+    <t>Compute Overtopping Discharge Rate per Unit Width Response (Eurotop)</t>
+  </si>
+  <si>
+    <t>compute_q_vol</t>
+  </si>
+  <si>
+    <t>Compute Overtopping Discharge Volume Unit Width Response (Eurotop) (RB3 Only)</t>
+  </si>
+  <si>
+    <t>compute_damaging_depth</t>
+  </si>
+  <si>
+    <t>Comput Damaging Depth Response</t>
+  </si>
+  <si>
+    <t>compute_damaging_depth_Ks</t>
   </si>
   <si>
     <t>Shielding Parameter To Use For Damaging Depths</t>
   </si>
   <si>
-    <t>compute_damaging_depth_Ks</t>
-  </si>
-  <si>
-    <t>Comput Damaging Depth Response</t>
-  </si>
-  <si>
-    <t>compute_damaging_depth</t>
-  </si>
-  <si>
-    <t>Compute Overtopping Discharge Volume Unit Width Response (Eurotop) (RB3 Only)</t>
-  </si>
-  <si>
-    <t>compute_q_vol</t>
-  </si>
-  <si>
-    <t>Compute Overtopping Discharge Rate per Unit Width Response (Eurotop)</t>
-  </si>
-  <si>
-    <t>compute_q</t>
-  </si>
-  <si>
-    <t>Compute Run-up Response (Eurotop)</t>
-  </si>
-  <si>
-    <t>compute_r2p</t>
-  </si>
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>Units</t>
-  </si>
-  <si>
-    <t>Field Names</t>
-  </si>
-  <si>
-    <t>Model Variable Symbol</t>
-  </si>
-  <si>
-    <t>Structure Responses</t>
-  </si>
-  <si>
-    <t>Roughness Coefficient, 2 for grass; 1 for concrete, asphalt, or closed blocks; 0.9 for basalt or placed revetment blocks; 0.8 for stepped structure; Table 6.2 from EurOtop (2018) (rubble mound )</t>
-  </si>
-  <si>
-    <t>roughness_ifactor</t>
-  </si>
-  <si>
-    <t>[Figure VI-5-11 CEM]</t>
-  </si>
-  <si>
-    <t>Mean Value Of Structure Notational Permeability Coefficient (P)</t>
-  </si>
-  <si>
-    <t>cem_P</t>
-  </si>
-  <si>
-    <t>[kg/m^3]</t>
-  </si>
-  <si>
-    <t>Water Density</t>
-  </si>
-  <si>
-    <t>water_density</t>
-  </si>
-  <si>
-    <t>[kg]</t>
-  </si>
-  <si>
-    <t>Seaside Stone Mass</t>
-  </si>
-  <si>
-    <t>seaside_mass</t>
-  </si>
-  <si>
-    <t>Armor Immersed Relative Density Delta</t>
-  </si>
-  <si>
-    <t>armor_delta</t>
-  </si>
-  <si>
-    <t>Structure Properties</t>
-  </si>
-  <si>
-    <t>[m]</t>
-  </si>
-  <si>
-    <t>Mound Landward Slope (cota)</t>
-  </si>
-  <si>
-    <t>leeside_slope</t>
-  </si>
-  <si>
-    <t>Mound/Berm Seaward Slope (cota)</t>
-  </si>
-  <si>
-    <t>seaside_slope</t>
-  </si>
-  <si>
-    <t>Mound Toe Elevation (Negative Below Datum Zero)</t>
-  </si>
-  <si>
-    <t>toe_elevation</t>
-  </si>
-  <si>
-    <t>Crest Width/Wall Width</t>
-  </si>
-  <si>
-    <t>crest_width</t>
-  </si>
-  <si>
-    <t>Crest Elevation/Top of Wall Elevation</t>
-  </si>
-  <si>
-    <t>crest_elevation</t>
-  </si>
-  <si>
-    <t>Plot hazard curve cross section plots (0 - Off, 1 - On)</t>
-  </si>
-  <si>
-    <t>pros_plot_hc_xsec</t>
-  </si>
-  <si>
-    <t>Plot RB1 priority datasets responses comparison (0 - Off, 1 - On)</t>
-  </si>
-  <si>
-    <t>pros_plot_prioty_comp</t>
-  </si>
-  <si>
-    <t>Structure Geometry</t>
-  </si>
-  <si>
-    <t>Plot forcing hazard curves with corresponding POT sample (0 - Off, 1 - On)</t>
-  </si>
-  <si>
-    <t>pros_plot_forcing_hc_w_pot</t>
-  </si>
-  <si>
-    <t>Plot individual responses hazard curves (0 - Off, 1 - On)</t>
-  </si>
-  <si>
-    <t>pros_plot_hc</t>
-  </si>
-  <si>
-    <t>none</t>
-  </si>
-  <si>
-    <t>Tidal file used to randomly sample tidal values for storm SWL. (Relative Path)</t>
-  </si>
-  <si>
-    <t>tide_file</t>
-  </si>
-  <si>
-    <t>Use AEP or AEF for hazard curves (1 - AEP, 0-AEF)</t>
-  </si>
-  <si>
-    <t>pros_use_aep</t>
-  </si>
-  <si>
-    <t>Chicago_files\CHS-GLMH_XH_SimBslc0_Post0_SP37697_Timeseries.zip</t>
-  </si>
-  <si>
-    <t>CHS Zip Folder or Custom Modeling .mat File (Relative Path)</t>
-  </si>
-  <si>
-    <t>chs_zip</t>
-  </si>
-  <si>
-    <t>Compute Hazard for Waves and WL (1 - On, 2 - Off)</t>
-  </si>
-  <si>
-    <t>pros_compute_forcing_HC</t>
-  </si>
-  <si>
-    <t>StormSim: Probabilistic Run-up, Overtopping &amp; Stone Sizing (PROS)</t>
-  </si>
-  <si>
-    <t>m</t>
-  </si>
-  <si>
-    <t>CHS savepoint depth (Will be used if not found in h5)</t>
-  </si>
-  <si>
-    <t>chs_sp_depth</t>
-  </si>
-  <si>
-    <t>hrs</t>
-  </si>
-  <si>
-    <t>Storm duration.</t>
-  </si>
-  <si>
-    <t>storm_duration</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>StormSim Project Forcing Data</t>
-  </si>
-  <si>
-    <t>Define Reference case_name To Load project_forcing From</t>
-  </si>
-  <si>
-    <t>ref_case_name</t>
-  </si>
-  <si>
-    <t>Load project_forcing StormSim File From Other case_name Under The Same project_name (0- Sample New Storms/1-Load Previous Storm Suite)</t>
-  </si>
-  <si>
-    <t>load_project_forcing</t>
-  </si>
-  <si>
-    <t>Generate output visualizations (0 - Off, 1 - On)</t>
-  </si>
-  <si>
-    <t>create_plots</t>
-  </si>
-  <si>
-    <t>[years]</t>
-  </si>
-  <si>
-    <t>Number Of Years To Be Simulated In A Life Cycle</t>
-  </si>
-  <si>
-    <t>mcs_nYears</t>
-  </si>
-  <si>
-    <t>Create Wave Height Priority Peaks Dataset (WLP)  (0 - Off / 1 - On). (Requires peaks and timeseries files)</t>
-  </si>
-  <si>
-    <t>create_whp</t>
-  </si>
-  <si>
-    <t>Number Of Life Cycles</t>
-  </si>
-  <si>
-    <t>mcs_nLC</t>
-  </si>
-  <si>
-    <t>Create Water Level Priority Peaks Dataset (WLP)  (0 - Off / 1 - On). (Requires peaks and timeseries files)</t>
-  </si>
-  <si>
-    <t>create_wlp</t>
-  </si>
-  <si>
-    <t>Include forcing timeseries files as part of the analysis.  (0 - Off / 1 - On)</t>
-  </si>
-  <si>
-    <t>use_timeseries</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t>StormSim: Monte Carlo Simulation (MCS) Module Inputs</t>
-  </si>
-  <si>
-    <t>Include forcing peaks files as part of the analysis.  (0 - Off / 1 - On)</t>
-  </si>
-  <si>
-    <t>use_peaks</t>
-  </si>
-  <si>
-    <t>Apply Depth Limitation To Waves  (0 - Off / 1 - On)</t>
-  </si>
-  <si>
-    <t>apply_depth_limitation</t>
-  </si>
-  <si>
-    <t>Apply random tide to storm SWL (0 - Off / 1 - On)</t>
-  </si>
-  <si>
-    <t>apply_random_tides</t>
-  </si>
-  <si>
-    <t>Sea level rise applied as vertical offset to SWL.</t>
-  </si>
-  <si>
-    <t>swl_slr</t>
-  </si>
-  <si>
-    <t>XC</t>
-  </si>
-  <si>
-    <t>Storm sampling scheme to use for project. (XC,TC or CC)</t>
-  </si>
-  <si>
-    <t>storm_sampling</t>
-  </si>
-  <si>
-    <t>Structure type  (Levee - 1, Floodwalls - 2, Rubblemound - 3)</t>
-  </si>
-  <si>
-    <t>struc_type</t>
-  </si>
-  <si>
-    <t>StormSim workflow to call for project. (1 - StormSim:PROS , 3- StormSim:LCS, 4- StormSim: PROS Frequency Base (FB))</t>
-  </si>
-  <si>
-    <t>workflow</t>
-  </si>
-  <si>
-    <t>[84 90]</t>
-  </si>
-  <si>
-    <t>Percentiles to compute CLs (max 4, 50 is already being calculated)</t>
-  </si>
-  <si>
-    <t>project_CLs</t>
-  </si>
-  <si>
-    <t>IGLD85</t>
-  </si>
-  <si>
-    <t>Project output datum. (Still not implemented. Used for plot title currently)</t>
-  </si>
-  <si>
-    <t>project_datum</t>
-  </si>
-  <si>
-    <t>SS_Outputs_7175_T3</t>
-  </si>
-  <si>
-    <t>StormSim Project output folder.</t>
-  </si>
-  <si>
-    <t>outfolder</t>
-  </si>
-  <si>
-    <t>Seawall_existing</t>
-  </si>
-  <si>
-    <t>Case Name</t>
-  </si>
-  <si>
-    <t>case_name</t>
-  </si>
-  <si>
-    <t>R7175_T3</t>
-  </si>
-  <si>
-    <t>Structure/Trasnsect ID</t>
-  </si>
-  <si>
-    <t>struc_id</t>
-  </si>
-  <si>
-    <t>Chicago Shoreline GRR</t>
-  </si>
-  <si>
-    <t>Project name</t>
-  </si>
-  <si>
-    <t>project_name</t>
-  </si>
-  <si>
-    <t>StormSim Project General Inputs</t>
-  </si>
-  <si>
-    <t>compute_wave_transmission</t>
-  </si>
-  <si>
-    <t>Compute wave transmission (eurotop)</t>
-  </si>
-  <si>
-    <t>Bottom Slope To Use For Damaging Depths (tanb)</t>
-  </si>
-  <si>
-    <t>chs_dependencies</t>
-  </si>
-  <si>
-    <t>CHS regional dependencies folder</t>
-  </si>
-  <si>
-    <t>..\CHS_Dependencies</t>
-  </si>
-  <si>
-    <t>compute_dn50_lcbw</t>
-  </si>
-  <si>
-    <t>Compute Seaward Median Stone Size Response (Low Crested Breakwater)</t>
+    <t>offshore_slope</t>
+  </si>
+  <si>
+    <t>Offshore slope (cota)</t>
   </si>
 </sst>
 </file>
@@ -533,7 +530,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -690,11 +687,42 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -799,6 +827,17 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1112,7 +1151,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{710E9416-AE2D-4233-9805-411704AE5E86}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:I60"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1127,71 +1166,71 @@
     <col min="9" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="44" t="s">
-        <v>122</v>
+        <v>0</v>
       </c>
       <c r="B1" s="41"/>
       <c r="C1" s="41"/>
       <c r="D1" s="41"/>
       <c r="F1" s="43" t="s">
-        <v>88</v>
+        <v>1</v>
       </c>
       <c r="G1" s="42"/>
       <c r="H1" s="42" t="s">
-        <v>87</v>
+        <v>2</v>
       </c>
       <c r="I1" s="42" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>68</v>
+        <v>4</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="I2" s="10" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
-        <v>121</v>
+        <v>8</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>120</v>
+        <v>9</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D3" s="18" t="s">
-        <v>119</v>
+        <v>11</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>82</v>
+        <v>12</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>81</v>
+        <v>13</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I3" s="6">
         <v>1000</v>
@@ -1199,25 +1238,25 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>118</v>
+        <v>14</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>117</v>
+        <v>15</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>116</v>
+        <v>16</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>78</v>
+        <v>17</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>77</v>
+        <v>18</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>76</v>
+        <v>19</v>
       </c>
       <c r="I4" s="2">
         <v>50</v>
@@ -1225,89 +1264,89 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>115</v>
+        <v>20</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>113</v>
+        <v>22</v>
       </c>
       <c r="F5" s="42"/>
       <c r="G5" s="42"/>
       <c r="H5" s="42"/>
       <c r="I5" s="42"/>
     </row>
-    <row r="6" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
-        <v>112</v>
+        <v>23</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>111</v>
+        <v>24</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>110</v>
+        <v>25</v>
       </c>
       <c r="F6" s="37" t="s">
-        <v>61</v>
+        <v>26</v>
       </c>
       <c r="G6" s="36"/>
       <c r="H6" s="36"/>
       <c r="I6" s="36"/>
     </row>
-    <row r="7" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
-        <v>109</v>
+        <v>27</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>108</v>
+        <v>28</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>107</v>
+        <v>29</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>106</v>
+        <v>30</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>105</v>
+        <v>31</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>104</v>
+        <v>32</v>
       </c>
       <c r="F8" s="34" t="s">
-        <v>60</v>
+        <v>33</v>
       </c>
       <c r="G8" s="20" t="s">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="H8" s="19" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I8" s="18">
         <v>1</v>
@@ -1315,25 +1354,25 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>103</v>
+        <v>35</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>102</v>
+        <v>36</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D9" s="2">
         <v>1</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I9" s="2">
         <v>0</v>
@@ -1341,25 +1380,25 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>101</v>
+        <v>39</v>
       </c>
       <c r="B10" s="26" t="s">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="C10" s="25" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D10" s="24">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I10" s="2">
         <v>1</v>
@@ -1367,25 +1406,25 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>99</v>
+        <v>43</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>98</v>
+        <v>44</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>97</v>
+        <v>45</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>47</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I11" s="2">
         <v>1</v>
@@ -1393,51 +1432,51 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>96</v>
+        <v>48</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>95</v>
+        <v>49</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="D12" s="2">
         <v>176.45</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I12" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
-        <v>94</v>
+        <v>53</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>93</v>
+        <v>54</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D13" s="2">
         <v>0</v>
       </c>
       <c r="F13" s="31" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="G13" s="17" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="H13" s="15" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I13" s="30">
         <v>1</v>
@@ -1445,13 +1484,13 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>92</v>
+        <v>57</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>91</v>
+        <v>58</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D14" s="2">
         <v>1</v>
@@ -1459,13 +1498,13 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>90</v>
+        <v>59</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>89</v>
+        <v>60</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D15" s="2">
         <v>0</v>
@@ -1473,13 +1512,13 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>86</v>
+        <v>61</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>85</v>
+        <v>62</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D16" s="2">
         <v>1</v>
@@ -1487,13 +1526,13 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>83</v>
+        <v>64</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D17" s="2">
         <v>0</v>
@@ -1501,13 +1540,13 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D18" s="2">
         <v>0</v>
@@ -1515,13 +1554,13 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D19" s="2">
         <v>1</v>
@@ -1529,30 +1568,30 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D20" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="31" t="s">
         <v>71</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D21" s="30" t="s">
-        <v>51</v>
+        <v>73</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1561,37 +1600,37 @@
       <c r="C22" s="39"/>
       <c r="D22" s="39"/>
     </row>
-    <row r="23" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="38" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B23" s="33"/>
       <c r="C23" s="33"/>
       <c r="D23" s="33"/>
     </row>
-    <row r="24" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="11" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>68</v>
+        <v>4</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="21" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="B25" s="20" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="C25" s="35" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="D25" s="18">
         <v>1</v>
@@ -1599,13 +1638,13 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="21" t="s">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="B26" s="20" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="C26" s="35" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="D26" s="18">
         <v>2.46</v>
@@ -1613,44 +1652,44 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="21" t="s">
-        <v>126</v>
+        <v>81</v>
       </c>
       <c r="B27" s="20" t="s">
-        <v>127</v>
+        <v>82</v>
       </c>
       <c r="C27" s="35" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D27" s="18" t="s">
-        <v>128</v>
+        <v>83</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>58</v>
+        <v>84</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>57</v>
+        <v>85</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>56</v>
+        <v>86</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>53</v>
+        <v>87</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>52</v>
+        <v>88</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>51</v>
+        <v>73</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1659,37 +1698,37 @@
       <c r="C30" s="33"/>
       <c r="D30" s="33"/>
     </row>
-    <row r="31" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="23" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="B31" s="32"/>
       <c r="C31" s="32"/>
       <c r="D31" s="32"/>
     </row>
-    <row r="32" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="11" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="21" t="s">
-        <v>41</v>
+        <v>90</v>
       </c>
       <c r="B33" s="29" t="s">
-        <v>40</v>
+        <v>91</v>
       </c>
       <c r="C33" s="28" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="D33" s="27">
         <v>180.1</v>
@@ -1697,13 +1736,13 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>39</v>
+        <v>92</v>
       </c>
       <c r="B34" s="26" t="s">
-        <v>38</v>
+        <v>93</v>
       </c>
       <c r="C34" s="25" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="D34" s="24">
         <v>0.3</v>
@@ -1711,13 +1750,13 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>37</v>
+        <v>94</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="D35" s="2">
         <v>-1</v>
@@ -1725,13 +1764,13 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>35</v>
+        <v>96</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>34</v>
+        <v>97</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D36" s="2">
         <v>3</v>
@@ -1739,83 +1778,84 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>32</v>
+        <v>99</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D37" s="2">
         <v>3</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="23"/>
-      <c r="B38" s="23"/>
-      <c r="C38" s="23"/>
-      <c r="D38" s="23"/>
-    </row>
-    <row r="39" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="22" t="s">
-        <v>30</v>
-      </c>
-      <c r="B39" s="13"/>
-      <c r="C39" s="13"/>
-      <c r="D39" s="13"/>
-    </row>
-    <row r="40" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B40" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="C40" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="D40" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="B41" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="C41" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="D41" s="18">
+    <row r="38" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="45" t="s">
+        <v>129</v>
+      </c>
+      <c r="B38" s="46" t="s">
+        <v>130</v>
+      </c>
+      <c r="C38" s="47" t="s">
+        <v>10</v>
+      </c>
+      <c r="D38" s="48">
+        <f>1/8</f>
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="23"/>
+      <c r="B39" s="23"/>
+      <c r="C39" s="23"/>
+      <c r="D39" s="23"/>
+    </row>
+    <row r="40" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="B40" s="13"/>
+      <c r="C40" s="13"/>
+      <c r="D40" s="13"/>
+    </row>
+    <row r="41" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B41" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D41" s="10" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" s="21" t="s">
+        <v>101</v>
+      </c>
+      <c r="B42" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="C42" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D42" s="18">
         <v>1.65</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B42" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D42" s="2">
-        <v>1000</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>24</v>
+        <v>103</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>23</v>
+        <v>104</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>22</v>
+        <v>105</v>
       </c>
       <c r="D43" s="2">
         <v>1000</v>
@@ -1823,83 +1863,83 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>21</v>
+        <v>106</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>20</v>
+        <v>107</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>19</v>
+        <v>108</v>
       </c>
       <c r="D44" s="2">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="D45" s="2">
         <v>0.4</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="B45" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="C45" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D45" s="14">
+    <row r="46" spans="1:4" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="B46" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="C46" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D46" s="14">
         <v>0.9</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" s="13"/>
-      <c r="B46" s="13"/>
-      <c r="C46" s="13"/>
-      <c r="D46" s="13"/>
-    </row>
-    <row r="47" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="B47" s="1"/>
-      <c r="C47" s="1"/>
-      <c r="D47" s="1"/>
-    </row>
-    <row r="48" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B48" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="C48" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="D48" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="B49" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D49" s="2">
-        <v>1</v>
+    <row r="47" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="13"/>
+      <c r="B47" s="13"/>
+      <c r="C47" s="13"/>
+      <c r="D47" s="13"/>
+    </row>
+    <row r="48" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="B48" s="1"/>
+      <c r="C48" s="1"/>
+      <c r="D48" s="1"/>
+    </row>
+    <row r="49" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B49" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C49" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D49" s="10" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
-        <v>11</v>
+        <v>115</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>10</v>
+        <v>116</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D50" s="2">
         <v>1</v>
@@ -1907,13 +1947,13 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D51" s="2">
         <v>1</v>
@@ -1921,13 +1961,13 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
-        <v>9</v>
+        <v>119</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>8</v>
+        <v>120</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D52" s="2">
         <v>1</v>
@@ -1935,13 +1975,13 @@
     </row>
     <row r="53" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>7</v>
+        <v>121</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>6</v>
+        <v>122</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D53" s="2">
         <v>1</v>
@@ -1949,44 +1989,44 @@
     </row>
     <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
-        <v>5</v>
+        <v>123</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>4</v>
+        <v>124</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D54" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
-        <v>3</v>
+        <v>125</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>2</v>
+        <v>126</v>
       </c>
       <c r="C55" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D55" s="2">
         <v>0</v>
-      </c>
-      <c r="D55" s="2">
-        <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D56" s="2">
         <v>1</v>
-      </c>
-      <c r="B56" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D56" s="2">
-        <v>8</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -1997,28 +2037,10 @@
     </row>
     <row r="60" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <sheetProtection formatColumns="0" selectLockedCells="1"/>
   <protectedRanges>
-    <protectedRange sqref="I3:I4 I8" name="Range1_1"/>
-    <protectedRange sqref="D41:D45" name="Range1_1_4"/>
-    <protectedRange sqref="D14 D16:D18 D9:D12 D6" name="Range1_1_1"/>
-    <protectedRange sqref="D8 D15" name="Range1_1_1_1"/>
-    <protectedRange sqref="D13" name="Range1_1_2"/>
-    <protectedRange sqref="D3" name="Range1_1_3_2"/>
-    <protectedRange sqref="D4" name="Range1_1_8"/>
-    <protectedRange sqref="D5" name="Range1_1_7"/>
-    <protectedRange sqref="D7" name="Range1_1_5"/>
-    <protectedRange sqref="D25" name="Range1_1_3_3"/>
-    <protectedRange sqref="D29" name="Range1_1_2_1_1"/>
-    <protectedRange sqref="D26:D27" name="Range1_1_5_2"/>
-    <protectedRange sqref="D28" name="Range1_1_8_1_1"/>
-    <protectedRange sqref="D33" name="Range1_1_3_1_3"/>
-    <protectedRange sqref="D34" name="Range1_1_3_1_4"/>
-    <protectedRange sqref="D35" name="Range1_1_3_1_5"/>
-    <protectedRange sqref="D36" name="Range1_1_3_1_7"/>
-    <protectedRange sqref="D37" name="Range1_1_3_1_8"/>
+    <protectedRange sqref="D38" name="Range1_1_3_1_8"/>
   </protectedRanges>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>